--- a/diseases/d120/1980-1984.xlsx
+++ b/diseases/d120/1980-1984.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14518,9 +14413,6 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="S72" t="inlineStr">

--- a/diseases/d120/1980-1984.xlsx
+++ b/diseases/d120/1980-1984.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1980-02-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1980-02</t>
+          <t>1980-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1162,40 +1162,45 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1297,12 +1302,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1980-02-01</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1980-02</t>
+          <t>1980-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1402,34 +1407,39 @@
         </is>
       </c>
       <c r="AN5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1531,12 +1541,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1980-03-01</t>
+          <t>1980-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1980-03</t>
+          <t>1980-02</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1552,40 +1562,45 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1687,12 +1702,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1980-03-01</t>
+          <t>1980-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1980-03</t>
+          <t>1980-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1792,34 +1807,39 @@
         </is>
       </c>
       <c r="AN7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1921,12 +1941,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1980-04-01</t>
+          <t>1980-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1980-04</t>
+          <t>1980-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1942,40 +1962,45 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2077,12 +2102,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1980-04-01</t>
+          <t>1980-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1980-04</t>
+          <t>1980-03</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2182,34 +2207,39 @@
         </is>
       </c>
       <c r="AN9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2311,12 +2341,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1980-05-01</t>
+          <t>1980-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1980-05</t>
+          <t>1980-04</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2332,40 +2362,45 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2467,12 +2502,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1980-05-01</t>
+          <t>1980-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1980-05</t>
+          <t>1980-04</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2572,34 +2607,39 @@
         </is>
       </c>
       <c r="AN11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2701,12 +2741,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1980-06-01</t>
+          <t>1980-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1980-06</t>
+          <t>1980-05</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2722,40 +2762,45 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2857,12 +2902,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1980-06-01</t>
+          <t>1980-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1980-06</t>
+          <t>1980-05</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2962,34 +3007,39 @@
         </is>
       </c>
       <c r="AN13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3091,19 +3141,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1980-07-01</t>
+          <t>1980-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1980-07</t>
+          <t>1980-06</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3112,40 +3162,45 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3247,19 +3302,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1980-07-01</t>
+          <t>1980-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1980-07</t>
+          <t>1980-06</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3352,34 +3407,39 @@
         </is>
       </c>
       <c r="AN15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3481,19 +3541,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1980-08-01</t>
+          <t>1980-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1980-08</t>
+          <t>1980-07</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3502,40 +3562,45 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3637,139 +3702,144 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1980-08-01</t>
+          <t>1980-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1980-08</t>
+          <t>1980-07</t>
         </is>
       </c>
       <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
         <v>0</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN17" t="b">
-        <v>1</v>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3871,12 +3941,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1980-09-01</t>
+          <t>1980-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1980-09</t>
+          <t>1980-08</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3892,40 +3962,45 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4027,12 +4102,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1980-09-01</t>
+          <t>1980-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1980-09</t>
+          <t>1980-08</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -4132,34 +4207,39 @@
         </is>
       </c>
       <c r="AN19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4261,61 +4341,66 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1980-10-01</t>
+          <t>1980-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1980-10</t>
+          <t>1980-09</t>
         </is>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
         <v>2</v>
       </c>
-      <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT20" t="n">
-        <v>1</v>
-      </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4417,139 +4502,144 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1980-10-01</t>
+          <t>1980-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1980-10</t>
+          <t>1980-09</t>
         </is>
       </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT21" t="n">
-        <v>1</v>
-      </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4651,19 +4741,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1980-11-01</t>
+          <t>1980-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1980-11</t>
+          <t>1980-10</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4672,40 +4762,45 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4807,139 +4902,144 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1980-11-01</t>
+          <t>1980-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1980-11</t>
+          <t>1980-10</t>
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
         <v>0</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN23" t="b">
-        <v>1</v>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5041,12 +5141,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1980-12-01</t>
+          <t>1980-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1980-12</t>
+          <t>1980-11</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -5062,40 +5162,45 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5197,12 +5302,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1980-12-01</t>
+          <t>1980-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1980-12</t>
+          <t>1980-11</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -5302,34 +5407,39 @@
         </is>
       </c>
       <c r="AN25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5431,19 +5541,19 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1980-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1980-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5452,40 +5562,45 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5587,19 +5702,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1980-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1980-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5692,34 +5807,39 @@
         </is>
       </c>
       <c r="AN27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5791,12 +5911,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5821,12 +5941,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5842,12 +5962,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5867,7 +5987,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5880,42 +6000,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5947,12 +6067,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5977,12 +6097,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1983-02-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1983-02</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5993,17 +6113,17 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -6018,12 +6138,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6033,7 +6153,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6068,12 +6188,12 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -6101,7 +6221,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6114,42 +6234,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6301,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6211,12 +6331,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -6232,12 +6352,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -6257,7 +6377,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -6270,42 +6390,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6457,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6367,12 +6487,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1983-03-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1983-03</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -6383,17 +6503,17 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -6408,12 +6528,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -6423,7 +6543,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6458,12 +6578,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -6491,7 +6611,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -6504,42 +6624,42 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6691,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6601,19 +6721,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6622,12 +6742,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -6647,7 +6767,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -6660,42 +6780,42 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6727,12 +6847,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6757,33 +6877,33 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1983-04-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1983-04</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -6798,12 +6918,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -6813,7 +6933,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -6848,12 +6968,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -6881,7 +7001,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -6894,42 +7014,42 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6991,19 +7111,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7012,40 +7132,45 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7147,139 +7272,144 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1983-05-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1983-05</t>
+          <t>1983-01</t>
         </is>
       </c>
       <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
         <v>0</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7381,19 +7511,19 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -7402,40 +7532,45 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7537,19 +7672,19 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1983-06-01</t>
+          <t>1983-02-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1983-06</t>
+          <t>1983-02</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -7642,34 +7777,39 @@
         </is>
       </c>
       <c r="AN37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7771,12 +7911,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -7792,40 +7932,45 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7927,12 +8072,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1983-07-01</t>
+          <t>1983-03-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-03</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -8032,34 +8177,39 @@
         </is>
       </c>
       <c r="AN39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8161,12 +8311,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -8182,40 +8332,45 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8317,12 +8472,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983-04-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1983-08</t>
+          <t>1983-04</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -8422,34 +8577,39 @@
         </is>
       </c>
       <c r="AN41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8551,12 +8711,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -8572,40 +8732,45 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8707,12 +8872,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1983-09-01</t>
+          <t>1983-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1983-09</t>
+          <t>1983-05</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -8812,34 +8977,39 @@
         </is>
       </c>
       <c r="AN43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8941,19 +9111,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8962,40 +9132,45 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9097,139 +9272,144 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1983-10-01</t>
+          <t>1983-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1983-10</t>
+          <t>1983-06</t>
         </is>
       </c>
       <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
         <v>0</v>
       </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN45" t="b">
-        <v>1</v>
-      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9331,12 +9511,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -9352,40 +9532,45 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9487,12 +9672,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1983-11-01</t>
+          <t>1983-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1983-11</t>
+          <t>1983-07</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -9592,34 +9777,39 @@
         </is>
       </c>
       <c r="AN47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9721,61 +9911,66 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
         <v>2</v>
       </c>
-      <c r="O48" t="n">
-        <v>2</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT48" t="n">
-        <v>1</v>
-      </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9877,139 +10072,144 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1983-12-01</t>
+          <t>1983-08-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1983-12</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
         <v>2</v>
       </c>
-      <c r="O49" t="n">
-        <v>2</v>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT49" t="n">
-        <v>1</v>
-      </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10111,12 +10311,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -10132,40 +10332,45 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10267,12 +10472,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1983-09-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1983-09</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -10372,34 +10577,39 @@
         </is>
       </c>
       <c r="AN51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10501,12 +10711,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -10522,40 +10732,45 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10657,12 +10872,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1984-02-01</t>
+          <t>1983-10-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1984-02</t>
+          <t>1983-10</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10762,34 +10977,39 @@
         </is>
       </c>
       <c r="AN53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10891,12 +11111,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -10912,40 +11132,45 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11047,12 +11272,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1984-03-01</t>
+          <t>1983-11-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1984-03</t>
+          <t>1983-11</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -11152,34 +11377,39 @@
         </is>
       </c>
       <c r="AN55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11281,19 +11511,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11302,40 +11532,45 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11437,19 +11672,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1984-04-01</t>
+          <t>1983-12-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1984-04</t>
+          <t>1983-12</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11542,34 +11777,39 @@
         </is>
       </c>
       <c r="AN57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -11641,12 +11881,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11671,19 +11911,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11692,12 +11932,12 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -11717,7 +11957,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11730,42 +11970,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11797,12 +12037,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11827,33 +12067,33 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1984-05-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1984-05</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -11868,12 +12108,12 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -11883,7 +12123,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11918,12 +12158,12 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -11951,7 +12191,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D120_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -11964,42 +12204,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12061,19 +12301,19 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12082,40 +12322,45 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12217,19 +12462,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1984-06-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1984-06</t>
+          <t>1984-01</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12322,34 +12567,39 @@
         </is>
       </c>
       <c r="AN61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12451,12 +12701,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -12472,40 +12722,45 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12607,12 +12862,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1984-07-01</t>
+          <t>1984-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1984-07</t>
+          <t>1984-02</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -12712,34 +12967,39 @@
         </is>
       </c>
       <c r="AN63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12841,19 +13101,19 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12862,40 +13122,45 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -12997,19 +13262,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1984-08-01</t>
+          <t>1984-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1984-08</t>
+          <t>1984-03</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13102,34 +13367,39 @@
         </is>
       </c>
       <c r="AN65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13231,19 +13501,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13252,40 +13522,45 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13387,139 +13662,144 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1984-09-01</t>
+          <t>1984-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1984-09</t>
+          <t>1984-04</t>
         </is>
       </c>
       <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
         <v>0</v>
       </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
-        <v>1</v>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13621,19 +13901,19 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13642,40 +13922,45 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13777,19 +14062,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1984-10-01</t>
+          <t>1984-05-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1984-10</t>
+          <t>1984-05</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -13882,34 +14167,39 @@
         </is>
       </c>
       <c r="AN69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14011,19 +14301,19 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14032,40 +14322,45 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14167,139 +14462,144 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1984-11-01</t>
+          <t>1984-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1984-11</t>
+          <t>1984-06</t>
         </is>
       </c>
       <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
         <v>0</v>
       </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Tetanus</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN71" t="b">
-        <v>1</v>
-      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14401,12 +14701,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -14422,40 +14722,45 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_104_MONTHLY</t>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14557,12 +14862,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1984-12-01</t>
+          <t>1984-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1984-12</t>
+          <t>1984-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -14662,72 +14967,2077 @@
         </is>
       </c>
       <c r="AN73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1984-08-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1984-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
         <v>1</v>
       </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP73" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1984-08-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1984-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="inlineStr">
         <is>
           <t>SER_NO_FHI_104_MONTHLY</t>
         </is>
       </c>
-      <c r="AT73" t="n">
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1984-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1984-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1984-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1984-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1984-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1984-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
         <v>1</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV73" t="inlineStr">
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW73" t="inlineStr">
+      <c r="AW78" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AX78" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
+      <c r="AY78" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA73" t="inlineStr">
+      <c r="BA78" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB73" t="inlineStr">
+      <c r="BB78" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC73" t="inlineStr">
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1984-10-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1984-10</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1984-11-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1984-11</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>tetanus</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1984-12</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_104_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_TETA_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -14849,7 +17159,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -14859,7 +17169,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -14879,7 +17189,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -14889,7 +17199,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -14911,7 +17221,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
